--- a/12622730().xlsx
+++ b/12622730().xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87079169-673C-4A6A-BF9B-8A45C7693672}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251142C7-0DC5-483B-93DF-63F81C6A6F6D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,10 +585,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2615,7 +2611,7 @@
         <v>10</v>
       </c>
       <c r="D39" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E39" s="14">
         <v>12</v>
@@ -2631,11 +2627,11 @@
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>902</v>
+        <v>932</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>538</v>
+        <v>508</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>67</v>
